--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-message.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.1</t>
+    <t>5.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T10:10:10+00:00</t>
+    <t>2026-02-13T11:55:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}medcom-messaging-1:The MessageHeader resource shall conform to medcom-messaging-messageHeader profile {entry[0].resource.conformsTo('http://medcomfhir.dk/ig/messaging/StructureDefinition/medcom-messaging-messageHeader')}medcom-messaging-2:There shall be at least one Provenance resource in a MedCom message {entry.resource.ofType(Provenance).exists()}medcom-careCommunication-1:The MessageHeader shall conform to medcom-careCommunication-messageHeader profile {entry[0].resource.conformsTo('http://medcomfhir.dk/ig/carecommunication/StructureDefinition/medcom-careCommunication-messageHeader')}medcom-careCommunication-2:Entry shall contain exactly one Patient resource {entry.where(resource.is(Patient)).count() = 1}medcom-careCommunication-4:There shall exist a practitioner given and family name when using a PractitionerRole. {entry.resource.ofType(Practitioner).name.exists()}medcom-careCommunication-3:All Provenance resources shall be of the type medcom-careCommunication-provenance profile {entry.resource.ofType(Provenance).all(conformsTo('http://medcomfhir.dk/ig/carecommunication/StructureDefinition/medcom-careCommunication-provenance'))}medcom-careCommunication-12:If a specific recipient is present, at least one of the organisations that the referenced CareTeam or Practitioner/PractitionerRole belongs to MUST equal the organisation referenced in MessageHeader.receiver.
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}medcom-messaging-2:There shall be at least one Provenance resource in a MedCom message {entry.resource.ofType(Provenance).exists()}medcom-careCommunication-1:The MessageHeader shall be the medcom-careCommunication-messageHeader {entry[0].resource.ofType(MessageHeader).meta.profile.startsWith('http://medcomfhir.dk/ig/carecommunication/StructureDefinition/medcom-careCommunication-messageHeader')}medcom-careCommunication-2:Entry shall contain exactly one Patient resource {entry.where(resource.is(Patient)).count() = 1}medcom-careCommunication-4:There shall exist a practitioner given and family name when using a PractitionerRole. {entry.resource.ofType(Practitioner).name.exists()}medcom-careCommunication-3:All Provenance resources shall be of the type medcom-careCommunication-provenance profile {entry.resource.ofType(Provenance).all(meta.profile.startsWith('http://medcomfhir.dk/ig/carecommunication/StructureDefinition/medcom-careCommunication-provenance'))}medcom-careCommunication-12:If a specific recipient is present, at least one of the organisations that the referenced CareTeam or Practitioner/PractitionerRole belongs to MUST equal the organisation referenced in MessageHeader.receiver.
 If no specific recipient is present, this rule is not evaluated. {Bundle.entry.resource.ofType(Communication).recipient.reference.resolve().managingOrganization.reference.resolve() = %resource.entry.resource.ofType(MessageHeader).destination.receiver.reference.resolve() or Bundle.entry.resource.ofType(Communication).recipient.reference.resolve().organization.reference.resolve() = %resource.entry.resource.ofType(MessageHeader).destination.receiver.reference.resolve() or Bundle.entry.resource.ofType(Communication).recipient.exists().not()}medcom-careCommunication-11:If a specific sender is present, at least one of the organisations that the
  referenced CareTeam or Practitioner/PractitionerRole belongs to MUST equal the organisation referenced in MessageHeader.sender.
 If no specific sender extension is present, this rule is not evaluated. {Bundle.entry.resource.ofType(Communication).extension.value.reference.resolve().managingOrganization.reference.resolve()
@@ -1458,7 +1458,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>85</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>130</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>174</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>188</v>
       </c>
@@ -6788,12 +6788,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN49">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-message.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.2</t>
+    <t>5.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T11:55:29+00:00</t>
+    <t>2026-06-03T09:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-message.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.3</t>
+    <t>5.0.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:32:39+00:00</t>
+    <t>2026-06-05T08:11:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,7 +273,9 @@
         = %resource.entry.resource.ofType(MessageHeader).sender.reference.resolve()
     or Bundle.entry.resource.ofType(Communication).extension.value.reference.resolve().organization.reference.resolve()
         = %resource.entry.resource.ofType(MessageHeader).sender.reference.resolve()
-    or Bundle.entry.resource.ofType(Communication).extension.exists().not()}medcom-careCommunication-13:All PractitionerRole resources shall have a reference to an instance of a Practitioner resource. {Bundle.entry.resource.ofType(PractitionerRole).practitioner.reference.exists()}</t>
+    or Bundle.entry.resource.ofType(Communication).extension.exists().not()}medcom-careCommunication-13:All PractitionerRole resources shall have a reference to an instance of a Practitioner resource. {Bundle.entry.resource.ofType(PractitionerRole).practitioner.reference.exists()}medcom-careCommunication-15:If an Encounter resource is present in the bundle, there must be a reference to it in Communication.encounter. If no Encounter is present, Communication.encounter must not be populated. {iif(Bundle.entry.resource.ofType(Encounter).exists(),
+                Bundle.entry.resource.ofType(Encounter).id = Bundle.entry.resource.ofType(Communication).encounter.reference.resolve().id,
+                Bundle.entry.resource.ofType(Communication).encounter.exists().not())}</t>
   </si>
   <si>
     <t>N/A</t>
